--- a/stories/arbres/ATOM-VIV.PLA.001-02.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila est à la cuisine avec maman. Un petit pot de basilic est près de la fenêtre. Les feuilles sont un peu molles. Maman dit : la plante a besoin d'eau. Elle a besoin de lumière. Lila prend le petit arrosoir. Maman, l'adulte, tient aussi l'anse. Elles versent un peu d'eau. La terre devient sombre. La lumière de la fenêtre arrive. Lila touche une feuille, tout doux. Maman dit : on arrose avec un adulte.</t>
+          <t>Lila est à la cuisine avec maman. Un petit pot de basilic est près de la fenêtre. Les feuilles sont un peu molles. La plante a besoin d'eau. Elle a besoin de lumière. Lila prend le petit arrosoir. Maman, l'adulte, tient aussi l'anse. Elles versent un peu d'eau. La terre devient sombre. La lumière de la fenêtre arrive. Lila touche une feuille, tout doux. On arrose avec un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lila est à la cuisine avec maman. Un petit pot de basilic est près de la fenêtre. Les feuilles sont un peu molles.
+maman|La plante a besoin d'eau. Elle a besoin de lumière.
+narrateur|Lila prend le petit arrosoir. Maman, l'adulte, tient aussi l'anse. Elles versent un peu d'eau. La terre devient sombre. La lumière de la fenêtre arrive. Lila touche une feuille, tout doux.
+maman|On arrose avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le basilic a soif. Que fait Lila avec maman ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a versé l'eau. La lumière est là. Maman, l'adulte, était avec elle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Lila range l'arrosoir. Le basilic sent bon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-02.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 maman|On arrose avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Le basilic a soif. Que fait Lila avec maman ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Lila a versé l'eau. La lumière est là. Maman, l'adulte, était avec elle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1838,7 @@
           <t>narrateur|Lila range l'arrosoir. Le basilic sent bon.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2049,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.PLA.001-02.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le basilic de Lila à la fenêtre</t>
+          <t>La chenille du basilic</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut sentir une feuille de basilic. Une chenille est dessus. On regarde, on n'écrase pas. Maman la pose sur une plante sauvage. Puis elles arrosent.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila est à la cuisine avec maman. Un petit pot de basilic est près de la fenêtre. Les feuilles sont un peu molles. La plante a besoin d'eau. Elle a besoin de lumière. Lila prend le petit arrosoir. Maman, l'adulte, tient aussi l'anse. Elles versent un peu d'eau. La terre devient sombre. La lumière de la fenêtre arrive. Lila touche une feuille, tout doux. On arrose avec un adulte.</t>
+          <t>Une mouche tape le carreau de la cuisine. Le carreau vibre, tout petit. Ça sent le pain d'hier, un peu rassis. Le basilic est dans son pot gris. Mila vit ici, avec maman. Tu veux une feuille pour la tomate ? Oui. Je veux la sentir d'abord. En ce moment, Mila se hausse. Ses orteils cherchent le rebord du meuble. Une feuille brille, bien large. Celle-là. Mila approche le nez. Quelque chose bouge sur le vert. Il y a un ver ! Ce n'est pas un ver. C'est une chenille, toute rayée. Elle avance comme un soufflet. On la regarde. On ne l'écrase pas, d'accord ? Elle mange ma feuille. Un tout petit bout. On va lui trouver une autre plante ? Dehors ? Dehors, une plante sauvage. Maman glisse un carton sous la feuille. La chenille marche sur le carton. Mila ouvre la porte de la cour. L'air sent la poussière chaude. Une plante rêche pousse contre le mur. Ici. Elle a des feuilles plus dures. La chenille glisse sur le vert sauvage. Elle est partie. Oui. Ton basilic a encore soif, tu as vu ? Les feuilles du pot pendent un peu. La terre est claire, presque grise. Il veut de l'eau. On rentre l'arrosoir ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila est à la cuisine avec maman. Un petit pot de basilic est près de la fenêtre. Les feuilles sont un peu molles. Maman dit : la plante a besoin d'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Elle a besoin de lumière. Lila prend le petit arrosoir. Maman, l'adulte, tient aussi l'anse. Elles versent un peu d'eau. La terre devient sombre. La lumière de la fenêtre arrive. Lila touche une feuille, tout doux. Maman dit : on arrose avec un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une mouche tape le carreau de la cuisine. Le carreau vibre, tout petit. Ça sent le pain d'hier, un peu rassis. Le basilic est dans son pot gris. Mila vit ici, avec maman. Tu veux une feuille pour la tomate ? Oui. Je veux la sentir d'abord. En ce moment, Mila se hausse. Ses orteils cherchent le rebord du meuble. Une feuille brille, bien large. Celle-là. Mila approche le nez. Quelque chose bouge sur le vert. Il y a un ver ! Ce n'est pas un ver. C'est une chenille, toute rayée. Elle avance comme un soufflet. On la regarde. On ne l'écrase pas, d'accord ? Elle mange ma feuille. Un tout petit bout. On va lui trouver une autre plante ? Dehors ? Dehors, une plante sauvage. Maman glisse un carton sous la feuille. La chenille marche sur le carton. Mila ouvre la porte de la cour. L'air sent la poussière chaude. Une plante rêche pousse contre le mur. Ici. Elle a des feuilles plus dures. La chenille glisse sur le vert sauvage. Elle est partie. Oui. Ton basilic a encore soif, tu as vu ? Les feuilles du pot pendent un peu. La terre est claire, presque grise. Il veut de l'eau. On rentre l'arrosoir ?</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Lila est à la cuisine avec maman. Un petit pot de basilic est près de la fenêtre. Les feuilles sont un peu molles.
-maman|La plante a besoin d'eau. Elle a besoin de lumière.
-narrateur|Lila prend le petit arrosoir. Maman, l'adulte, tient aussi l'anse. Elles versent un peu d'eau. La terre devient sombre. La lumière de la fenêtre arrive. Lila touche une feuille, tout doux.
-maman|On arrose avec un adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une mouche tape le carreau de la cuisine.
+narrateur|Le carreau vibre, tout petit.
+narrateur|Ça sent le pain d'hier, un peu rassis.
+narrateur|Le basilic est dans son pot gris.
+narrateur|Mila vit ici, avec maman.
+maman|Tu veux une feuille pour la tomate ?
+enfant-f|Oui.
+enfant-f|Je veux la sentir d'abord.
+narrateur|En ce moment, Mila se hausse.
+narrateur|Ses orteils cherchent le rebord du meuble.
+narrateur|Une feuille brille, bien large.
+enfant-f|Celle-là.
+narrateur|Mila approche le nez.
+narrateur|Quelque chose bouge sur le vert.
+enfant-f|Il y a un ver !
+narrateur|Ce n'est pas un ver.
+narrateur|C'est une chenille, toute rayée.
+narrateur|Elle avance comme un soufflet.
+maman|On la regarde.
+maman|On ne l'écrase pas, d'accord ?
+enfant-f|Elle mange ma feuille.
+maman|Un tout petit bout.
+maman|On va lui trouver une autre plante ?
+enfant-f|Dehors ?
+maman|Dehors, une plante sauvage.
+narrateur|Maman glisse un carton sous la feuille.
+narrateur|La chenille marche sur le carton.
+narrateur|Mila ouvre la porte de la cour.
+narrateur|L'air sent la poussière chaude.
+narrateur|Une plante rêche pousse contre le mur.
+maman|Ici.
+maman|Elle a des feuilles plus dures.
+narrateur|La chenille glisse sur le vert sauvage.
+enfant-f|Elle est partie.
+maman|Oui.
+maman|Ton basilic a encore soif, tu as vu ?
+narrateur|Les feuilles du pot pendent un peu.
+narrateur|La terre est claire, presque grise.
+enfant-f|Il veut de l'eau.
+maman|On rentre l'arrosoir ?</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1390,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le basilic a soif. Que fait Lila avec maman ?</t>
+          <t>Le basilic a soif. Que fait Mila avec maman ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le basilic a soif. Que fait Lila avec maman ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le basilic a soif. Que fait Mila avec maman ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1378,7 +1425,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elles versent de l'eau. Que fait Lila ?</t>
+          <t>Elles versent de l'eau. Que fait Mila ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1474,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1499,10 +1546,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le basilic a soif. Que fait Lila avec maman ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le basilic a soif.
+narrateur|Que fait Mila avec maman ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,12 +1574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila a versé l'eau. La lumière est là. Maman, l'adulte, était avec elle.</t>
+          <t>Mila tient l'arrosoir à deux mains. Maman pose les doigts sur l'anse. L'eau tombe, un filet mince. La terre devient sombre, tout de suite. Elle boit. Oui. Un peu, pas trop. Une goutte reste sur une feuille. Elle brille comme un grain. Je peux sentir, maintenant ? La grande feuille, oui. Mila froisse tout doux le vert. L'odeur saute, poivrée, chaude. Ça pique ! C'est le basilic. Merci, Mila. Tu as regardé la chenille. Tu n'as pas écrasé. Elle mange dehors. Sur sa plante à elle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila a versé l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. La lumière est là. Maman, l'adulte, était avec elle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila tient l'arrosoir à deux mains. Maman pose les doigts sur l'anse. L'eau tombe, un filet mince. La terre devient sombre, tout de suite. Elle boit. Oui. Un peu, pas trop. Une goutte reste sur une feuille. Elle brille comme un grain. Je peux sentir, maintenant ? La grande feuille, oui. Mila froisse tout doux le vert. L'odeur saute, poivrée, chaude. Ça pique ! C'est le basilic. Merci, Mila. Tu as regardé la chenille. Tu n'as pas écrasé. Elle mange dehors. Sur sa plante à elle.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1595,7 +1642,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1671,10 +1718,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lila a versé l'eau. La lumière est là. Maman, l'adulte, était avec elle.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila tient l'arrosoir à deux mains.
+narrateur|Maman pose les doigts sur l'anse.
+narrateur|L'eau tombe, un filet mince.
+narrateur|La terre devient sombre, tout de suite.
+enfant-f|Elle boit.
+maman|Oui.
+maman|Un peu, pas trop.
+narrateur|Une goutte reste sur une feuille.
+narrateur|Elle brille comme un grain.
+enfant-f|Je peux sentir, maintenant ?
+maman|La grande feuille, oui.
+narrateur|Mila froisse tout doux le vert.
+narrateur|L'odeur saute, poivrée, chaude.
+enfant-f|Ça pique !
+maman|C'est le basilic.
+maman|Merci, Mila.
+maman|Tu as regardé la chenille.
+maman|Tu n'as pas écrasé.
+enfant-f|Elle mange dehors.
+maman|Sur sa plante à elle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,12 +1764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Lila range l'arrosoir. Le basilic sent bon.</t>
+          <t>Maman coupe une feuille pour la tomate. Le couteau fait un tout petit clic. Et la chenille ? On va voir, si tu veux. Dans la cour, le mur est chaud. La plante sauvage sent l'herbe amère. Elle est encore là. La chenille mange, très lente. Chacun sa feuille. Le basilic pour nous. Celle-là pour elle. D'accord. Mila pose un doigt près, sans toucher. La chenille ne s'arrête pas. On laisse ? On laisse. Le basilic, derrière la vitre, tient plus droit. Une goutte sèche sur le rebord.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila range l'arrosoir. Le basilic sent bon.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman coupe une feuille pour la tomate. Le couteau fait un tout petit clic. Et la chenille ? On va voir, si tu veux. Dans la cour, le mur est chaud. La plante sauvage sent l'herbe amère. Elle est encore là. La chenille mange, très lente. Chacun sa feuille. Le basilic pour nous. Celle-là pour elle. D'accord. Mila pose un doigt près, sans toucher. La chenille ne s'arrête pas. On laisse ? On laisse. Le basilic, derrière la vitre, tient plus droit. Une goutte sèche sur le rebord.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,7 +1832,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1900,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Lila range l'arrosoir. Le basilic sent bon.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman coupe une feuille pour la tomate.
+narrateur|Le couteau fait un tout petit clic.
+enfant-f|Et la chenille ?
+maman|On va voir, si tu veux.
+narrateur|Dans la cour, le mur est chaud.
+narrateur|La plante sauvage sent l'herbe amère.
+enfant-f|Elle est encore là.
+narrateur|La chenille mange, très lente.
+maman|Chacun sa feuille.
+maman|Le basilic pour nous.
+maman|Celle-là pour elle.
+enfant-f|D'accord.
+narrateur|Mila pose un doigt près, sans toucher.
+narrateur|La chenille ne s'arrête pas.
+maman|On laisse ?
+enfant-f|On laisse.
+narrateur|Le basilic, derrière la vitre, tient plus droit.
+narrateur|Une goutte sèche sur le rebord.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1863,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila rentre. La tomate attend, rouge, sur l'assiette. Ça sent le basilic. Oui. La feuille que tu voulais. La feuille sent encore le soleil.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila rentre. La tomate attend, rouge, sur l'assiette. Ça sent le basilic. Oui. La feuille que tu voulais. La feuille sent encore le soleil.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1924,14 +2005,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2003,10 +2084,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Mila rentre.
+narrateur|La tomate attend, rouge, sur l'assiette.
+enfant-f|Ça sent le basilic.
+maman|Oui.
+maman|La feuille que tu voulais.
+narrateur|La feuille sent encore le soleil.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2063,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-02.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine puis cour, basilic à la fenêtre</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lila, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
